--- a/src/main/import/fixtures/planilla-ejemplo.xlsx
+++ b/src/main/import/fixtures/planilla-ejemplo.xlsx
@@ -635,6 +635,9 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
       <c r="C4" t="s">
         <v>63</v>
       </c>
